--- a/CI_Index_Template.xlsx
+++ b/CI_Index_Template.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI Index" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PN Variants" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CI Index'!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PN Variants'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -536,57 +538,78 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>•  Where MBSE is used, CI parent-child relationships mirror the model decomposition (PROC-001 §5.2.1); record the model element ID and the ATA chapter or S1000D SNS reference for each CI.</t>
+          <t>•  The 'PN Variants' sheet records the CI-to-PIN variant mapping for one-CI/multiple-PN verdicts per [XXX-CM-GUIDE-001] §6: one row per variant PIN, keyed by CI ID, with the per-variant interface callout and effectivity.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>•  Safety-critical CIs (criterion (b) / SMS hazard log): set Safety-Critical = Y and record the hazard log reference. These are CM floor items (Floor ID F01).</t>
+          <t>•  Where MBSE is used, CI parent-child relationships mirror the model decomposition (PROC-001 §5.2.1); record the model element ID and the ATA chapter or S1000D SNS reference for each CI.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>•  Selection Assessment Ref points to the completed PROC-001 Appendix A checklist for the CI.</t>
+          <t>•  Safety-critical CIs (criterion (b) / SMS hazard log): set Safety-Critical = Y and record the hazard log reference. These are CM floor items (Floor ID F01).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>•  Baseline columns record the status or establishment date of each baseline for the CI (e.g., 'Established 2026-03-14' or 'Planned CDR+60d').</t>
+          <t>•  Selection Assessment Ref points to the completed PROC-001 Appendix A checklist for the CI.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>•  Baseline columns record the status or establishment date of each baseline for the CI (e.g., 'Established 2026-03-14' or 'Planned CDR+60d').</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>•  De-designated CIs are not deleted: set Status = De-designated and retain the row for traceability.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Column notes</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>•  PIN is not unique across rows: per [XXX-CM-GUIDE-001], one part number may legitimately map to multiple CIs (same physical item instantiated in subsystems performing distinct functions) — each instantiation gets its own CI row carrying the same PIN. Conversely, one CI may carry multiple PN variants: keep the base/representative PIN on the CI row and record the full variant mapping on the 'PN Variants' sheet.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>•  Same-CI-or-separate verdicts come from [XXX-CM-GUIDE-001]; cite the triggered gate(s) in the Selection Assessment Ref rationale. Verdicts held pending MBSE model disposition (guide §5.3, gate G10) are NOT entered in this index until the model and CI structure agree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Column notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>•  CI ID: program-unique identifier for the CI (not the PIN). PIN: part or identifying number per design activity convention, with CAGE forming the full identification.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>•  Control: Acquirer-controlled CIs are those the Acquirer specifies, baselines, and controls; lower-tier items are Supplier-controlled.</t>
         </is>
@@ -1904,6 +1927,285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CI ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Variant PIN</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Variant Description</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Interface Callout (spec/ICD ref)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Effectivity</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CI-0021</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>ACT-2230-002</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Elevator actuator, baseline build</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>PS-2230 §3.3.1</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>AV units 1–12</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Base variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CI-0021</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>ACT-2230-004</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Elevator actuator, revised connector</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>PS-2230 §3.3.2 (per-variant callout)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>AV units 13+</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Non-interchangeable connector; one CI per GUIDE-001 (no gate triggered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
